--- a/astro-site/public/dl/burger-joint-checklist-templates/03-burger-restaurant-manager-checklist.xlsx
+++ b/astro-site/public/dl/burger-joint-checklist-templates/03-burger-restaurant-manager-checklist.xlsx
@@ -2213,9 +2213,9 @@
       <c r="A12" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>Deep-clean the griddle (take apart if possible)</t>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>Griddle: check the surface and thermostat with a surface thermometer, and deep-clean the grease trough</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
@@ -2240,9 +2240,9 @@
       <c r="A13" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>Full fryer oil change</t>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>Fryer boil-out: drain, clean with fryer cleaner and refill with fresh oil, per the manufacturer (the oil itself is changed whenever the TPM tester says, not once a month)</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
